--- a/naver-place-crawler/results_health/평택_PT.xlsx
+++ b/naver-place-crawler/results_health/평택_PT.xlsx
@@ -421,8 +421,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>여성전용헬스 PT 플래너휘트니스 비전점</t>
+          <t>아세로짐 용죽점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>planner-22@naver.com</t>
+          <t>acero_yong@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-656-6637</t>
+          <t>0507-1412-0716</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 709 삼육빌딩 4층</t>
+          <t>경기 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/planner_fitness2/</t>
+          <t>https://www.instagram.com/acero_yong</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ir3m</t>
+          <t>https://talk.naver.com/ct/w6ejzs8</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="Q2" t="n">
-        <v>479</v>
+        <v>222</v>
       </c>
       <c r="R2" t="n">
-        <v>651</v>
+        <v>346</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1816388747</t>
+          <t>1478339886</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816388747</t>
+          <t>https://m.place.naver.com/place/1478339886</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,34 +662,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>여성전용 24시 헬스PT 그레이스짐</t>
+          <t>365일 24시 라이트짐 평택역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>minho8802@naver.com</t>
+          <t>lightgym3871@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>031-653-0788</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로64번길 32</t>
+          <t>경기 평택시 평택로32번길 34 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kQTJd</t>
+          <t>https://blog.naver.com/lightgym3871/224146200506</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,27 +705,27 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc4qhk</t>
+          <t>https://talk.naver.com/ct/w4pf7a</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1240</v>
+        <v>1648</v>
       </c>
       <c r="Q3" t="n">
-        <v>1196</v>
+        <v>819</v>
       </c>
       <c r="R3" t="n">
-        <v>2436</v>
+        <v>2467</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>38320515</t>
+          <t>1099573478</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38320515</t>
+          <t>https://m.place.naver.com/place/1099573478</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,34 +756,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>평택PT 헬스 버닝핏</t>
+          <t>여성전용 24시 헬스PT 그레이스짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>im_pt@naver.com</t>
+          <t>minho8802@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1379-1245</t>
+          <t>031-653-0788</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 평택시 조개터로5번길 8-17 1층</t>
+          <t>경기 평택시 평택로64번길 32</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/im_pt</t>
+          <t>http://pf.kakao.com/_kQTJd</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -797,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,27 +803,27 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40hdd</t>
+          <t>https://talk.naver.com/ct/wc4qhk</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>126</v>
+        <v>1244</v>
       </c>
       <c r="Q4" t="n">
-        <v>1566</v>
+        <v>1061</v>
       </c>
       <c r="R4" t="n">
-        <v>1692</v>
+        <v>2305</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1138820844</t>
+          <t>38320515</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138820844</t>
+          <t>https://m.place.naver.com/place/38320515</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,25 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>365일 24시 라이트짐 평택역점</t>
+          <t>헬스보이짐 비전점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lightgym3871@naver.com</t>
+          <t>healthboy08@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1410-3434</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로32번길 34 4층</t>
+          <t>경기 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lightgym3871/224146200506</t>
+          <t>https://blog.naver.com/healthboy08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pf7a</t>
+          <t>https://talk.naver.com/ct/wceqsz</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1630</v>
+        <v>766</v>
       </c>
       <c r="Q5" t="n">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="R5" t="n">
-        <v>2447</v>
+        <v>1586</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1099573478</t>
+          <t>1886642565</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099573478</t>
+          <t>https://m.place.naver.com/place/1886642565</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐 비전점</t>
+          <t>평택PT 헬스 버닝핏</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboy08@naver.com</t>
+          <t>im_pt@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1410-3434</t>
+          <t>0507-1379-1245</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
+          <t>경기 평택시 조개터로5번길 8-17 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy08</t>
+          <t>https://blog.naver.com/im_pt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wceqsz</t>
+          <t>https://talk.naver.com/ct/w40hdd</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>766</v>
+        <v>126</v>
       </c>
       <c r="Q6" t="n">
-        <v>813</v>
+        <v>1566</v>
       </c>
       <c r="R6" t="n">
-        <v>1579</v>
+        <v>1692</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1886642565</t>
+          <t>1138820844</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1886642565</t>
+          <t>https://m.place.naver.com/place/1138820844</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1050,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>제이에스PT 평택고덕점</t>
+          <t>모든핏PT 평택고덕점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jspt_pyeongtaek@naver.com</t>
+          <t>mombanpt@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1384-0394</t>
+          <t>0507-1400-3818</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 평택시 고덕국제4길 26 1층</t>
+          <t>경기 평택시 고덕국제7로 117 706호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jspt_pyeongtaekgodeok</t>
+          <t>https://blog.naver.com/mombanpt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42ocd</t>
+          <t>https://talk.naver.com/ct/w5v09h</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>165</v>
+        <v>99</v>
       </c>
       <c r="Q7" t="n">
-        <v>236</v>
+        <v>73</v>
       </c>
       <c r="R7" t="n">
-        <v>401</v>
+        <v>172</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1013603492</t>
+          <t>1906617322</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013603492</t>
+          <t>https://m.place.naver.com/place/1906617322</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1190,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46rjr</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1205,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q8" t="n">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="R8" t="n">
-        <v>679</v>
+        <v>716</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1230,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1303,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q9" t="n">
         <v>118</v>
       </c>
       <c r="R9" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1328,7 +1332,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="Q10" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="R10" t="n">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1495,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2851</v>
+        <v>2878</v>
       </c>
       <c r="Q11" t="n">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="R11" t="n">
-        <v>4091</v>
+        <v>4124</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1520,7 +1524,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/평택_PT.xlsx
+++ b/naver-place-crawler/results_health/평택_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="Q3" t="n">
         <v>819</v>
       </c>
       <c r="R3" t="n">
-        <v>2467</v>
+        <v>2470</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -820,10 +820,10 @@
         <v>1244</v>
       </c>
       <c r="Q4" t="n">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="R4" t="n">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1016,10 +1016,10 @@
         <v>126</v>
       </c>
       <c r="Q6" t="n">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="R6" t="n">
-        <v>1692</v>
+        <v>1697</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q8" t="n">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="R8" t="n">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,46 +1234,46 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한결같이, 필라테스</t>
+          <t>평택센텀정형외과의원</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hk_pilates_@naver.com</t>
+          <t>ptcentum_os@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1419-9699</t>
+          <t>0507-1333-0053</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 평택시 소사5길 32 2층 한결같이,필라테스</t>
+          <t>경기 평택시 평남로 937 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hk_pilates_</t>
+          <t>http://ptcentum.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1288,14 +1288,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4gyg6</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,17 +1299,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>184</v>
+        <v>584</v>
       </c>
       <c r="Q9" t="n">
-        <v>118</v>
+        <v>529</v>
       </c>
       <c r="R9" t="n">
-        <v>302</v>
+        <v>1113</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,56 +1318,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1425824440</t>
+          <t>1940036531</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1425824440</t>
+          <t>https://m.place.naver.com/place/1940036531</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>정형외과</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>평택센텀정형외과의원</t>
+          <t>넥스트짐 평택비전점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ptcentum_os@naver.com</t>
+          <t>nextgym05@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1333-0053</t>
+          <t>0507-1324-9680</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 937 2층</t>
+          <t>경기 평택시 평남로 862 로이드빌딩 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://ptcentum.com/</t>
+          <t>https://www.instagram.com/nextgym_05_official/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1386,28 +1382,32 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wa9rmy3</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>585</v>
+        <v>2883</v>
       </c>
       <c r="Q10" t="n">
-        <v>529</v>
+        <v>1248</v>
       </c>
       <c r="R10" t="n">
-        <v>1114</v>
+        <v>4131</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,51 +1416,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1940036531</t>
+          <t>1742730874</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1940036531</t>
+          <t>https://m.place.naver.com/place/1742730874</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>넥스트짐 평택비전점 헬스 PT</t>
+          <t>올웨이즈피트니스 비전점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nextgym05@naver.com</t>
+          <t>alwaysfit-@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1324-9680</t>
+          <t>031-652-9682</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 862 로이드빌딩 4층</t>
+          <t>경기 평택시 비전5로 20-52 4층 올웨이즈 피트니스 비전점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nextgym_05_official/</t>
+          <t>https://blog.naver.com/alwaysfit-</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,27 +1485,27 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wa9rmy3</t>
+          <t>https://talk.naver.com/ct/w5vdvz</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2878</v>
+        <v>249</v>
       </c>
       <c r="Q11" t="n">
-        <v>1246</v>
+        <v>233</v>
       </c>
       <c r="R11" t="n">
-        <v>4124</v>
+        <v>482</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1742730874</t>
+          <t>1376852137</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742730874</t>
+          <t>https://m.place.naver.com/place/1376852137</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/평택_PT.xlsx
+++ b/naver-place-crawler/results_health/평택_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -1140,394 +1140,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>두피,탈모관리</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>닥터모락 평택점</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>drmork-9@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>031-691-2096</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>경기 평택시 평택로32번길 24 201호</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://www.besttimes.co.kr/9225</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46rjr</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>151</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>572</v>
-      </c>
-      <c r="R8" t="n">
-        <v>723</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1061269101</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1061269101</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>정형외과</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>평택센텀정형외과의원</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ptcentum_os@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1333-0053</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>경기 평택시 평남로 937 2층</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>http://ptcentum.com/</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>584</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>529</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1113</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1940036531</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1940036531</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>넥스트짐 평택비전점 헬스 PT</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>nextgym05@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1324-9680</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>경기 평택시 평남로 862 로이드빌딩 4층</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nextgym_05_official/</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wa9rmy3</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>2883</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1248</v>
-      </c>
-      <c r="R10" t="n">
-        <v>4131</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1742730874</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1742730874</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>올웨이즈피트니스 비전점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>alwaysfit-@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>031-652-9682</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>경기 평택시 비전5로 20-52 4층 올웨이즈 피트니스 비전점</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/alwaysfit-</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vdvz</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>249</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>233</v>
-      </c>
-      <c r="R11" t="n">
-        <v>482</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1376852137</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1376852137</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver-place-crawler/results_health/평택_PT.xlsx
+++ b/naver-place-crawler/results_health/평택_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
+          <t>경기도 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w6ejzs8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -675,7 +671,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로32번길 34 4층</t>
+          <t>경기도 평택시 평택로32번길 34 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +696,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pf7a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -773,7 +765,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로64번길 32</t>
+          <t>경기도 평택시 평택로64번길 32</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,14 +790,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc4qhk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -871,7 +859,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
+          <t>경기도 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -896,14 +884,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wceqsz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -969,7 +953,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 평택시 조개터로5번길 8-17 1층</t>
+          <t>경기도 평택시 조개터로5번길 8-17 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,14 +978,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40hdd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1016,10 +996,10 @@
         <v>126</v>
       </c>
       <c r="Q6" t="n">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="R6" t="n">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1067,7 +1047,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 평택시 고덕국제7로 117 706호</t>
+          <t>경기도 평택시 고덕국제7로 117 706호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1092,14 +1072,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5v09h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1135,6 +1111,390 @@
         </is>
       </c>
       <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>두피,탈모관리</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>닥터모락 평택점</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>drmork-9@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>031-691-2096</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>경기 평택시 평택로32번길 24 201호</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.besttimes.co.kr/9225</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46rjr</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>575</v>
+      </c>
+      <c r="R8" t="n">
+        <v>726</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1061269101</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1061269101</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>한결같이, 필라테스</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>hk_pilates_@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1419-9699</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>경기 평택시 소사5길 32 2층 한결같이,필라테스</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hk_pilates_</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gyg6</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>120</v>
+      </c>
+      <c r="R9" t="n">
+        <v>306</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1425824440</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1425824440</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>정형외과</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>평택센텀정형외과의원</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ptcentum_os@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1333-0053</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>경기 평택시 평남로 937 2층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>http://ptcentum.com/</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>584</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>529</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1113</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1940036531</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1940036531</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>넥스트짐 평택비전점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>nextgym05@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1324-9680</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>경기도 평택시 평남로 862 로이드빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nextgym_05_official/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>2884</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1249</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4133</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1742730874</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1742730874</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/평택_PT.xlsx
+++ b/naver-place-crawler/results_health/평택_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -996,10 +996,10 @@
         <v>126</v>
       </c>
       <c r="Q6" t="n">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="R6" t="n">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1217,39 +1217,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한결같이, 필라테스</t>
+          <t>평택센텀정형외과의원</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hk_pilates_@naver.com</t>
+          <t>ptcentum_os@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1419-9699</t>
+          <t>0507-1333-0053</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 평택시 소사5길 32 2층 한결같이,필라테스</t>
+          <t>경기 평택시 평남로 937 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hk_pilates_</t>
+          <t>http://ptcentum.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1264,14 +1264,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4gyg6</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>186</v>
+        <v>584</v>
       </c>
       <c r="Q9" t="n">
-        <v>120</v>
+        <v>529</v>
       </c>
       <c r="R9" t="n">
-        <v>306</v>
+        <v>1113</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1425824440</t>
+          <t>1940036531</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1425824440</t>
+          <t>https://m.place.naver.com/place/1940036531</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1315,39 +1311,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>정형외과</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>평택센텀정형외과의원</t>
+          <t>넥스트짐 평택비전점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ptcentum_os@naver.com</t>
+          <t>nextgym05@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1333-0053</t>
+          <t>0507-1324-9680</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 937 2층</t>
+          <t>경기도 평택시 평남로 862 로이드빌딩 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://ptcentum.com/</t>
+          <t>https://www.instagram.com/nextgym_05_official/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1373,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>584</v>
+        <v>2884</v>
       </c>
       <c r="Q10" t="n">
-        <v>529</v>
+        <v>1249</v>
       </c>
       <c r="R10" t="n">
-        <v>1113</v>
+        <v>4133</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1940036531</t>
+          <t>1742730874</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1940036531</t>
+          <t>https://m.place.naver.com/place/1742730874</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1409,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>넥스트짐 평택비전점 헬스 PT</t>
+          <t>여성전용헬스 PT 플래너휘트니스 비전점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nextgym05@naver.com</t>
+          <t>planner-22@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1324-9680</t>
+          <t>031-656-6637</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 평택시 평남로 862 로이드빌딩 4층</t>
+          <t>경기도 평택시 평남로 709 삼육빌딩 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nextgym_05_official/</t>
+          <t>https://www.instagram.com/planner_fitness2/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2884</v>
+        <v>171</v>
       </c>
       <c r="Q11" t="n">
-        <v>1249</v>
+        <v>489</v>
       </c>
       <c r="R11" t="n">
-        <v>4133</v>
+        <v>660</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1742730874</t>
+          <t>1816388747</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742730874</t>
+          <t>https://m.place.naver.com/place/1816388747</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/평택_PT.xlsx
+++ b/naver-place-crawler/results_health/평택_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
+          <t>경기 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6ejzs8</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -646,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -671,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 평택시 평택로32번길 34 4층</t>
+          <t>경기 평택시 평택로32번길 34 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pf7a</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -711,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="Q3" t="n">
         <v>819</v>
       </c>
       <c r="R3" t="n">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -736,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -765,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 평택시 평택로64번길 32</t>
+          <t>경기 평택시 평택로64번길 32</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -790,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc4qhk</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -830,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -859,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
+          <t>경기 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -884,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wceqsz</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -924,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -953,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 평택시 조개터로5번길 8-17 1층</t>
+          <t>경기 평택시 조개터로5번길 8-17 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -978,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40hdd</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1018,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1067,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 평택시 고덕국제7로 117 706호</t>
+          <t>경기 평택시 고덕국제7로 117 706호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1072,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v09h</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1112,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1175,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1161,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1181,17 +1205,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
         <v>151</v>
       </c>
       <c r="Q8" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="R8" t="n">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1210,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1328,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1357,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 평택시 평남로 862 로이드빌딩 4층</t>
+          <t>경기 평택시 평남로 862 로이드빌딩 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1358,13 +1382,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wa9rmy3</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="Q10" t="n">
         <v>1249</v>
       </c>
       <c r="R10" t="n">
-        <v>4133</v>
+        <v>4134</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1398,7 +1426,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1455,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 평택시 평남로 709 삼육빌딩 4층</t>
+          <t>경기 평택시 평남로 709 삼육빌딩 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1452,10 +1480,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ir3m</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1492,7 +1524,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/평택_PT.xlsx
+++ b/naver-place-crawler/results_health/평택_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아세로짐 용죽점</t>
+          <t>365일 24시 라이트짐 평택역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>acero_yong@naver.com</t>
+          <t>lightgym3871@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1412-0716</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
+          <t>경기도 평택시 평택로32번길 34 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/acero_yong</t>
+          <t>https://blog.naver.com/lightgym3871/224146200506</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,19 +597,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w6ejzs8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>124</v>
+        <v>1650</v>
       </c>
       <c r="Q2" t="n">
-        <v>222</v>
+        <v>819</v>
       </c>
       <c r="R2" t="n">
-        <v>346</v>
+        <v>2469</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +632,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1478339886</t>
+          <t>1099573478</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478339886</t>
+          <t>https://m.place.naver.com/place/1099573478</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,30 +654,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>365일 24시 라이트짐 평택역점</t>
+          <t>여성전용 24시 헬스PT 그레이스짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lightgym3871@naver.com</t>
+          <t>minho8802@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>031-653-0788</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로32번길 34 4층</t>
+          <t>경기도 평택시 평택로64번길 32</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lightgym3871/224146200506</t>
+          <t>http://pf.kakao.com/_kQTJd</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,37 +691,33 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pf7a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1650</v>
+        <v>1244</v>
       </c>
       <c r="Q3" t="n">
-        <v>819</v>
+        <v>1060</v>
       </c>
       <c r="R3" t="n">
-        <v>2469</v>
+        <v>2304</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +726,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1099573478</t>
+          <t>38320515</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099573478</t>
+          <t>https://m.place.naver.com/place/38320515</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,34 +748,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>여성전용 24시 헬스PT 그레이스짐</t>
+          <t>헬스보이짐 비전점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>minho8802@naver.com</t>
+          <t>healthboy08@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>031-653-0788</t>
+          <t>0507-1410-3434</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로64번길 32</t>
+          <t>경기도 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kQTJd</t>
+          <t>https://blog.naver.com/healthboy08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -793,22 +785,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc4qhk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -817,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1244</v>
+        <v>766</v>
       </c>
       <c r="Q4" t="n">
-        <v>1060</v>
+        <v>820</v>
       </c>
       <c r="R4" t="n">
-        <v>2304</v>
+        <v>1586</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>38320515</t>
+          <t>1886642565</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38320515</t>
+          <t>https://m.place.naver.com/place/1886642565</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +842,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐 비전점</t>
+          <t>파인핏 5호점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboy08@naver.com</t>
+          <t>fine_fit5@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1410-3434</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
+          <t>경기도 평택시 평남로 1012 6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy08</t>
+          <t>https://blog.naver.com/fine_fit5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,14 +880,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wceqsz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>766</v>
+        <v>111</v>
       </c>
       <c r="Q5" t="n">
-        <v>820</v>
+        <v>147</v>
       </c>
       <c r="R5" t="n">
-        <v>1586</v>
+        <v>258</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +910,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1886642565</t>
+          <t>1150778118</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1886642565</t>
+          <t>https://m.place.naver.com/place/1150778118</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -969,7 +949,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 평택시 조개터로5번길 8-17 1층</t>
+          <t>경기도 평택시 조개터로5번길 8-17 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,14 +974,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40hdd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1016,10 +992,10 @@
         <v>126</v>
       </c>
       <c r="Q6" t="n">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="R6" t="n">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1045,34 +1021,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>두피,탈모관리</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>모든핏PT 평택고덕점</t>
+          <t>닥터모락 평택점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mombanpt@naver.com</t>
+          <t>drmork-9@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1400-3818</t>
+          <t>031-691-2096</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 평택시 고덕국제7로 117 706호</t>
+          <t>경기 평택시 평택로32번길 24 201호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mombanpt</t>
+          <t>https://www.besttimes.co.kr/9225</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1097,12 +1073,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v09h</t>
+          <t>https://talk.naver.com/ct/w46rjr</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="Q7" t="n">
-        <v>73</v>
+        <v>579</v>
       </c>
       <c r="R7" t="n">
-        <v>172</v>
+        <v>730</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1906617322</t>
+          <t>1061269101</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906617322</t>
+          <t>https://m.place.naver.com/place/1061269101</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,34 +1119,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두피,탈모관리</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>닥터모락 평택점</t>
+          <t>평택센텀정형외과의원</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>drmork-9@naver.com</t>
+          <t>ptcentum_os@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-691-2096</t>
+          <t>0507-1333-0053</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로32번길 24 201호</t>
+          <t>경기 평택시 평남로 937 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.besttimes.co.kr/9225</t>
+          <t>http://ptcentum.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1190,17 +1166,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46rjr</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>151</v>
+        <v>584</v>
       </c>
       <c r="Q8" t="n">
-        <v>576</v>
+        <v>529</v>
       </c>
       <c r="R8" t="n">
-        <v>727</v>
+        <v>1113</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1061269101</t>
+          <t>1940036531</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061269101</t>
+          <t>https://m.place.naver.com/place/1940036531</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1241,39 +1213,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>정형외과</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>평택센텀정형외과의원</t>
+          <t>넥스트짐 평택비전점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ptcentum_os@naver.com</t>
+          <t>nextgym05@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1333-0053</t>
+          <t>0507-1324-9680</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 937 2층</t>
+          <t>경기도 평택시 평남로 862 로이드빌딩 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://ptcentum.com/</t>
+          <t>https://www.instagram.com/nextgym_05_official/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1299,17 +1271,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>584</v>
+        <v>2885</v>
       </c>
       <c r="Q9" t="n">
-        <v>529</v>
+        <v>1249</v>
       </c>
       <c r="R9" t="n">
-        <v>1113</v>
+        <v>4134</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1940036531</t>
+          <t>1742730874</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1940036531</t>
+          <t>https://m.place.naver.com/place/1742730874</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1335,34 +1307,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>넥스트짐 평택비전점 헬스 PT</t>
+          <t>여성전용헬스 PT 플래너휘트니스 비전점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nextgym05@naver.com</t>
+          <t>planner-22@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1324-9680</t>
+          <t>031-656-6637</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 862 로이드빌딩 4층</t>
+          <t>경기도 평택시 평남로 709 삼육빌딩 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nextgym_05_official/</t>
+          <t>https://www.instagram.com/planner_fitness2/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1382,17 +1354,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wa9rmy3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2885</v>
+        <v>171</v>
       </c>
       <c r="Q10" t="n">
-        <v>1249</v>
+        <v>489</v>
       </c>
       <c r="R10" t="n">
-        <v>4134</v>
+        <v>660</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,113 +1384,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1742730874</t>
+          <t>1816388747</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742730874</t>
+          <t>https://m.place.naver.com/place/1816388747</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>여성전용헬스 PT 플래너휘트니스 비전점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>planner-22@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>031-656-6637</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>경기 평택시 평남로 709 삼육빌딩 4층</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/planner_fitness2/</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ir3m</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>171</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>489</v>
-      </c>
-      <c r="R11" t="n">
-        <v>660</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1816388747</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1816388747</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/평택_PT.xlsx
+++ b/naver-place-crawler/results_health/평택_PT.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -577,7 +577,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 평택시 평택로32번길 34 4층</t>
+          <t>경기 평택시 평택로32번길 34 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -602,10 +602,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pf7a</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -671,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 평택시 평택로64번길 32</t>
+          <t>경기 평택시 평택로64번길 32</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc4qhk</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -711,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="Q3" t="n">
         <v>1060</v>
       </c>
       <c r="R3" t="n">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -765,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
+          <t>경기 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -790,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wceqsz</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -808,10 +820,10 @@
         <v>766</v>
       </c>
       <c r="Q4" t="n">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="R4" t="n">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -855,7 +867,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 평택시 평남로 1012 6층</t>
+          <t>경기 평택시 평남로 1012 6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -880,10 +892,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wyyb</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -895,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q5" t="n">
         <v>147</v>
       </c>
       <c r="R5" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -949,7 +965,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 평택시 조개터로5번길 8-17 1층</t>
+          <t>경기 평택시 조개터로5번길 8-17 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -974,10 +990,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40hdd</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -992,10 +1012,10 @@
         <v>126</v>
       </c>
       <c r="Q6" t="n">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="R6" t="n">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1021,34 +1041,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두피,탈모관리</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>닥터모락 평택점</t>
+          <t>필라테스 재활PT체형교정 JIN운동센터 평택송탄점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>drmork-9@naver.com</t>
+          <t>dladmsfhr@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-691-2096</t>
+          <t>0507-1386-5781</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로32번길 24 201호</t>
+          <t>경기 평택시 이충로 49-31 삼원프라자 202호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.besttimes.co.kr/9225</t>
+          <t>https://youtube.com/@진운동센터</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1063,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1073,12 +1093,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46rjr</t>
+          <t>https://talk.naver.com/ct/w44lkf</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="Q7" t="n">
-        <v>579</v>
+        <v>535</v>
       </c>
       <c r="R7" t="n">
-        <v>730</v>
+        <v>756</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1061269101</t>
+          <t>1726616718</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061269101</t>
+          <t>https://m.place.naver.com/place/1726616718</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1119,39 +1139,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>정형외과</t>
+          <t>두피,탈모관리</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>평택센텀정형외과의원</t>
+          <t>닥터모락 평택점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ptcentum_os@naver.com</t>
+          <t>drmork-9@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1333-0053</t>
+          <t>031-691-2096</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 937 2층</t>
+          <t>경기 평택시 평택로32번길 24 201호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://ptcentum.com/</t>
+          <t>https://www.besttimes.co.kr/9225</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1161,33 +1181,37 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46rjr</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>584</v>
+        <v>151</v>
       </c>
       <c r="Q8" t="n">
-        <v>529</v>
+        <v>580</v>
       </c>
       <c r="R8" t="n">
-        <v>1113</v>
+        <v>731</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1940036531</t>
+          <t>1061269101</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1940036531</t>
+          <t>https://m.place.naver.com/place/1061269101</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1213,34 +1237,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>넥스트짐 평택비전점 헬스 PT</t>
+          <t>한결같이, 필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nextgym05@naver.com</t>
+          <t>hk_pilates_@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1324-9680</t>
+          <t>0507-1419-9699</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 평택시 평남로 862 로이드빌딩 4층</t>
+          <t>경기 평택시 소사5길 32 2층 한결같이,필라테스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nextgym_05_official/</t>
+          <t>https://www.instagram.com/hk_pilates_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1260,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gyg6</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1275,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2885</v>
+        <v>186</v>
       </c>
       <c r="Q9" t="n">
-        <v>1249</v>
+        <v>121</v>
       </c>
       <c r="R9" t="n">
-        <v>4134</v>
+        <v>307</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1742730874</t>
+          <t>1425824440</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742730874</t>
+          <t>https://m.place.naver.com/place/1425824440</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1307,39 +1335,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>여성전용헬스 PT 플래너휘트니스 비전점</t>
+          <t>평택센텀정형외과의원</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>planner-22@naver.com</t>
+          <t>ptcentum_os@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-656-6637</t>
+          <t>0507-1333-0053</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 평택시 평남로 709 삼육빌딩 4층</t>
+          <t>경기 평택시 평남로 937 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/planner_fitness2/</t>
+          <t>http://ptcentum.com/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1365,17 +1393,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>171</v>
+        <v>584</v>
       </c>
       <c r="Q10" t="n">
-        <v>489</v>
+        <v>529</v>
       </c>
       <c r="R10" t="n">
-        <v>660</v>
+        <v>1113</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1816388747</t>
+          <t>1940036531</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816388747</t>
+          <t>https://m.place.naver.com/place/1940036531</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/평택_PT.xlsx
+++ b/naver-place-crawler/results_health/평택_PT.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,30 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>365일 24시 라이트짐 평택역점</t>
+          <t>아세로짐 용죽점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lightgym3871@naver.com</t>
+          <t>acero_yong@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0507-1412-0716</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로32번길 34 4층</t>
+          <t>경기 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lightgym3871/224146200506</t>
+          <t>https://www.instagram.com/acero_yong</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -597,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -607,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pf7a</t>
+          <t>https://talk.naver.com/ct/w6ejzs8</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1650</v>
+        <v>124</v>
       </c>
       <c r="Q2" t="n">
-        <v>819</v>
+        <v>222</v>
       </c>
       <c r="R2" t="n">
-        <v>2469</v>
+        <v>346</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1099573478</t>
+          <t>1478339886</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099573478</t>
+          <t>https://m.place.naver.com/place/1478339886</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,34 +662,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>여성전용 24시 헬스PT 그레이스짐</t>
+          <t>365일 24시 라이트짐 평택역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>minho8802@naver.com</t>
+          <t>lightgym3871@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>031-653-0788</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로64번길 32</t>
+          <t>경기 평택시 평택로32번길 34 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kQTJd</t>
+          <t>https://blog.naver.com/lightgym3871/224146200506</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -705,27 +705,27 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc4qhk</t>
+          <t>https://talk.naver.com/ct/w4pf7a</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1245</v>
+        <v>1651</v>
       </c>
       <c r="Q3" t="n">
-        <v>1060</v>
+        <v>819</v>
       </c>
       <c r="R3" t="n">
-        <v>2305</v>
+        <v>2470</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>38320515</t>
+          <t>1099573478</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38320515</t>
+          <t>https://m.place.naver.com/place/1099573478</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -756,34 +756,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헬스보이짐 비전점</t>
+          <t>여성전용 24시 헬스PT 그레이스짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>healthboy08@naver.com</t>
+          <t>minho8802@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1410-3434</t>
+          <t>031-653-0788</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
+          <t>경기 평택시 평택로64번길 32</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy08</t>
+          <t>http://pf.kakao.com/_kQTJd</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wceqsz</t>
+          <t>https://talk.naver.com/ct/wc4qhk</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>766</v>
+        <v>1246</v>
       </c>
       <c r="Q4" t="n">
-        <v>822</v>
+        <v>1060</v>
       </c>
       <c r="R4" t="n">
-        <v>1588</v>
+        <v>2306</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1886642565</t>
+          <t>38320515</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1886642565</t>
+          <t>https://m.place.naver.com/place/38320515</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -854,25 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>파인핏 5호점</t>
+          <t>헬스보이짐 비전점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fine_fit5@naver.com</t>
+          <t>healthboy08@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1410-3434</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 1012 6층</t>
+          <t>경기 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fine_fit5</t>
+          <t>https://blog.naver.com/healthboy08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -897,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wyyb</t>
+          <t>https://talk.naver.com/ct/wceqsz</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -911,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>114</v>
+        <v>765</v>
       </c>
       <c r="Q5" t="n">
-        <v>147</v>
+        <v>822</v>
       </c>
       <c r="R5" t="n">
-        <v>261</v>
+        <v>1587</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1150778118</t>
+          <t>1886642565</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1150778118</t>
+          <t>https://m.place.naver.com/place/1886642565</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -948,29 +952,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>평택PT 헬스 버닝핏</t>
+          <t>파인핏 5호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>im_pt@naver.com</t>
+          <t>fine_fit5@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1379-1245</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 평택시 조개터로5번길 8-17 1층</t>
+          <t>경기 평택시 평남로 1012 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/im_pt</t>
+          <t>https://blog.naver.com/fine_fit5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40hdd</t>
+          <t>https://talk.naver.com/ct/w5wyyb</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="Q6" t="n">
-        <v>1575</v>
+        <v>148</v>
       </c>
       <c r="R6" t="n">
-        <v>1701</v>
+        <v>262</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,51 +1024,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1138820844</t>
+          <t>1150778118</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138820844</t>
+          <t>https://m.place.naver.com/place/1150778118</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>필라테스 재활PT체형교정 JIN운동센터 평택송탄점</t>
+          <t>평택PT 헬스 버닝핏</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dladmsfhr@naver.com</t>
+          <t>im_pt@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1386-5781</t>
+          <t>0507-1379-1245</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 평택시 이충로 49-31 삼원프라자 202호</t>
+          <t>경기 평택시 조개터로5번길 8-17 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://youtube.com/@진운동센터</t>
+          <t>https://blog.naver.com/im_pt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44lkf</t>
+          <t>https://talk.naver.com/ct/w40hdd</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>221</v>
+        <v>126</v>
       </c>
       <c r="Q7" t="n">
-        <v>535</v>
+        <v>1575</v>
       </c>
       <c r="R7" t="n">
-        <v>756</v>
+        <v>1701</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1726616718</t>
+          <t>1138820844</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726616718</t>
+          <t>https://m.place.naver.com/place/1138820844</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1230,46 +1230,46 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한결같이, 필라테스</t>
+          <t>평택센텀정형외과의원</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hk_pilates_@naver.com</t>
+          <t>ptcentum_os@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1419-9699</t>
+          <t>0507-1333-0053</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 평택시 소사5길 32 2층 한결같이,필라테스</t>
+          <t>경기 평택시 평남로 937 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hk_pilates_</t>
+          <t>http://ptcentum.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1284,14 +1284,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4gyg6</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1299,17 +1295,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>186</v>
+        <v>584</v>
       </c>
       <c r="Q9" t="n">
-        <v>121</v>
+        <v>529</v>
       </c>
       <c r="R9" t="n">
-        <v>307</v>
+        <v>1113</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,56 +1314,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1425824440</t>
+          <t>1940036531</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1425824440</t>
+          <t>https://m.place.naver.com/place/1940036531</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>정형외과</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>평택센텀정형외과의원</t>
+          <t>넥스트짐 평택비전점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ptcentum_os@naver.com</t>
+          <t>nextgym05@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1333-0053</t>
+          <t>0507-1324-9680</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 937 2층</t>
+          <t>경기 평택시 평남로 862 로이드빌딩 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://ptcentum.com/</t>
+          <t>https://www.instagram.com/nextgym_05_official/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1382,28 +1378,32 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wa9rmy3</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>584</v>
+        <v>2887</v>
       </c>
       <c r="Q10" t="n">
-        <v>529</v>
+        <v>1249</v>
       </c>
       <c r="R10" t="n">
-        <v>1113</v>
+        <v>4136</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,17 +1412,115 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1940036531</t>
+          <t>1742730874</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1940036531</t>
+          <t>https://m.place.naver.com/place/1742730874</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>여성전용헬스 PT 플래너휘트니스 비전점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>planner-22@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>031-656-6637</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>경기 평택시 평남로 709 삼육빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/planner_fitness2/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ir3m</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>489</v>
+      </c>
+      <c r="R11" t="n">
+        <v>660</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1816388747</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1816388747</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/평택_PT.xlsx
+++ b/naver-place-crawler/results_health/평택_PT.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
+          <t>경기도 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w6ejzs8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q2" t="n">
         <v>222</v>
       </c>
       <c r="R2" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -675,7 +671,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로32번길 34 4층</t>
+          <t>경기도 평택시 평택로32번길 34 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +696,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pf7a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -773,7 +765,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로64번길 32</t>
+          <t>경기도 평택시 평택로64번길 32</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,14 +790,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc4qhk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -817,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="Q4" t="n">
         <v>1060</v>
       </c>
       <c r="R4" t="n">
-        <v>2306</v>
+        <v>2304</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -871,7 +859,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
+          <t>경기도 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -896,14 +884,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wceqsz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -965,7 +949,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 1012 6층</t>
+          <t>경기도 평택시 평남로 1012 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -990,14 +974,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wyyb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1009,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q6" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="R6" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1063,7 +1043,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 평택시 조개터로5번길 8-17 1층</t>
+          <t>경기도 평택시 조개터로5번길 8-17 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1088,14 +1068,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40hdd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1110,10 +1086,10 @@
         <v>126</v>
       </c>
       <c r="Q7" t="n">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="R7" t="n">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1171,7 +1147,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1181,7 +1157,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1201,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
         <v>151</v>
       </c>
       <c r="Q8" t="n">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="R8" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1237,39 +1213,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>정형외과</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>평택센텀정형외과의원</t>
+          <t>한결같이, 필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ptcentum_os@naver.com</t>
+          <t>hk_pilates_@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1333-0053</t>
+          <t>0507-1419-9699</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 937 2층</t>
+          <t>경기 평택시 소사5길 32 2층 한결같이,필라테스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://ptcentum.com/</t>
+          <t>https://www.instagram.com/hk_pilates_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1284,10 +1260,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gyg6</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1295,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>584</v>
+        <v>187</v>
       </c>
       <c r="Q9" t="n">
-        <v>529</v>
+        <v>121</v>
       </c>
       <c r="R9" t="n">
-        <v>1113</v>
+        <v>308</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1940036531</t>
+          <t>1425824440</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1940036531</t>
+          <t>https://m.place.naver.com/place/1425824440</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1331,39 +1311,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>넥스트짐 평택비전점 헬스 PT</t>
+          <t>평택센텀정형외과의원</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nextgym05@naver.com</t>
+          <t>ptcentum_os@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1324-9680</t>
+          <t>0507-1333-0053</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 862 로이드빌딩 4층</t>
+          <t>경기 평택시 평남로 937 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nextgym_05_official/</t>
+          <t>http://ptcentum.com/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1378,32 +1358,28 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wa9rmy3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2887</v>
+        <v>584</v>
       </c>
       <c r="Q10" t="n">
-        <v>1249</v>
+        <v>530</v>
       </c>
       <c r="R10" t="n">
-        <v>4136</v>
+        <v>1114</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1742730874</t>
+          <t>1940036531</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742730874</t>
+          <t>https://m.place.naver.com/place/1940036531</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1429,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>여성전용헬스 PT 플래너휘트니스 비전점</t>
+          <t>넥스트짐 평택비전점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>planner-22@naver.com</t>
+          <t>nextgym05@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-656-6637</t>
+          <t>0507-1324-9680</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 평택시 평남로 709 삼육빌딩 4층</t>
+          <t>경기도 평택시 평남로 862 로이드빌딩 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/planner_fitness2/</t>
+          <t>https://www.instagram.com/nextgym_05_official/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1476,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ir3m</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1495,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>171</v>
+        <v>2893</v>
       </c>
       <c r="Q11" t="n">
-        <v>489</v>
+        <v>1251</v>
       </c>
       <c r="R11" t="n">
-        <v>660</v>
+        <v>4144</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1816388747</t>
+          <t>1742730874</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816388747</t>
+          <t>https://m.place.naver.com/place/1742730874</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/평택_PT.xlsx
+++ b/naver-place-crawler/results_health/평택_PT.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
+          <t>경기 평택시 용죽2로 32-45 5층 아세로짐 용죽점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6ejzs8</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q2" t="n">
         <v>222</v>
       </c>
       <c r="R2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -671,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 평택시 평택로32번길 34 4층</t>
+          <t>경기 평택시 평택로32번길 34 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pf7a</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -711,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1651</v>
+        <v>1654</v>
       </c>
       <c r="Q3" t="n">
         <v>819</v>
       </c>
       <c r="R3" t="n">
-        <v>2470</v>
+        <v>2473</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -736,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -765,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 평택시 평택로64번길 32</t>
+          <t>경기 평택시 평택로64번길 32</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -790,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc4qhk</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -808,10 +820,10 @@
         <v>1244</v>
       </c>
       <c r="Q4" t="n">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="R4" t="n">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -830,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -859,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
+          <t>경기 평택시 경기대로 271 패밀리타운 10층 ,9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -884,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wceqsz</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -924,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -949,7 +965,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 평택시 평남로 1012 6층</t>
+          <t>경기 평택시 평남로 1012 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -974,10 +990,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wyyb</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -989,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q6" t="n">
         <v>151</v>
       </c>
       <c r="R6" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1014,7 +1034,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1063,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 평택시 조개터로5번길 8-17 1층</t>
+          <t>경기 평택시 조개터로5번길 8-17 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1068,10 +1088,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40hdd</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1108,41 +1132,41 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두피,탈모관리</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>닥터모락 평택점</t>
+          <t>필라테스 재활PT체형교정 JIN운동센터 평택송탄점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>drmork-9@naver.com</t>
+          <t>dladmsfhr@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-691-2096</t>
+          <t>0507-1386-5781</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 평택시 평택로32번길 24 201호</t>
+          <t>경기 평택시 이충로 49-31 삼원프라자 202호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.besttimes.co.kr/9225</t>
+          <t>https://youtube.com/@진운동센터</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1157,7 +1181,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1167,12 +1191,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46rjr</t>
+          <t>https://talk.naver.com/ct/w44lkf</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1181,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="Q8" t="n">
-        <v>582</v>
+        <v>536</v>
       </c>
       <c r="R8" t="n">
-        <v>733</v>
+        <v>758</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,51 +1220,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1061269101</t>
+          <t>1726616718</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061269101</t>
+          <t>https://m.place.naver.com/place/1726616718</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>두피,탈모관리</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한결같이, 필라테스</t>
+          <t>닥터모락 평택점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hk_pilates_@naver.com</t>
+          <t>drmork-9@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1419-9699</t>
+          <t>031-691-2096</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 평택시 소사5길 32 2층 한결같이,필라테스</t>
+          <t>경기 평택시 평택로32번길 24 201호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hk_pilates_</t>
+          <t>https://www.besttimes.co.kr/9225</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1265,12 +1289,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4gyg6</t>
+          <t>https://talk.naver.com/ct/w46rjr</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="Q9" t="n">
-        <v>121</v>
+        <v>583</v>
       </c>
       <c r="R9" t="n">
-        <v>308</v>
+        <v>735</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1425824440</t>
+          <t>1061269101</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1425824440</t>
+          <t>https://m.place.naver.com/place/1061269101</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1373,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Q10" t="n">
         <v>530</v>
       </c>
       <c r="R10" t="n">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1398,7 +1422,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1451,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 평택시 평남로 862 로이드빌딩 4층</t>
+          <t>경기 평택시 평남로 862 로이드빌딩 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1452,13 +1476,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wa9rmy3</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2893</v>
+        <v>2901</v>
       </c>
       <c r="Q11" t="n">
         <v>1251</v>
       </c>
       <c r="R11" t="n">
-        <v>4144</v>
+        <v>4152</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1492,7 +1520,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
